--- a/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
+++ b/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>零件名称：</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>钣金快拆_5036</t>
+  </si>
+  <si>
+    <t>镀锌板</t>
   </si>
   <si>
     <t>大腿关节限位块</t>
@@ -866,7 +869,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -924,15 +927,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1349,48 +1343,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2843530</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>2072005</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="图片 28"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2533650" y="20250150"/>
-          <a:ext cx="2710180" cy="2052955"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -1409,7 +1361,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1451,7 +1403,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
+        <a:blip r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1475,90 +1427,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2843530</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>2077720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2495550" y="13963650"/>
-          <a:ext cx="2748280" cy="2058670"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2831465</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>2085975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2447925" y="16059150"/>
-          <a:ext cx="2783840" cy="2066925"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -1577,7 +1445,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1601,48 +1469,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2842260</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2057400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2457450" y="22332950"/>
-          <a:ext cx="2785110" cy="2051050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>24765</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
@@ -1661,7 +1487,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
+        <a:blip r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1703,7 +1529,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
+        <a:blip r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1727,33 +1553,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>37465</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2845435</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2083435</xdr:rowOff>
+      <xdr:colOff>2783205</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2068830</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPr id="14" name="图片 13"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
+        <a:blip r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2505075" y="26536650"/>
-          <a:ext cx="2740660" cy="2064385"/>
+          <a:off x="2457450" y="32841565"/>
+          <a:ext cx="2726055" cy="2031365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1769,19 +1595,187 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>37465</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2783205</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>2068830</xdr:rowOff>
+      <xdr:colOff>2752090</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2052320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="26527125"/>
+          <a:ext cx="2713990" cy="2042795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2773680</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2068195</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="图片 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="20250150"/>
+          <a:ext cx="2735580" cy="2049145"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2799080</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2067560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="图片 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2447925" y="13954125"/>
+          <a:ext cx="2751455" cy="2058035"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2835910</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2087880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="图片 20"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="22326600"/>
+          <a:ext cx="2797810" cy="2087880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2811780</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>2070100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1794,8 +1788,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="32841565"/>
-          <a:ext cx="2726055" cy="2031365"/>
+          <a:off x="2476500" y="16059150"/>
+          <a:ext cx="2735580" cy="2051050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2128,7 +2122,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2182,19 +2176,19 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
     </row>
     <row r="8" ht="13.5" spans="1:8">
       <c r="A8" s="1"/>
@@ -2458,13 +2452,13 @@
         <v>10</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H21" s="8"/>
     </row>
     <row r="22" ht="165" customHeight="1" spans="2:8">
       <c r="B22" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="22"/>
       <c r="D22" s="23">
@@ -2483,7 +2477,7 @@
     </row>
     <row r="23" ht="165" customHeight="1" spans="2:8">
       <c r="B23" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="9">
@@ -2501,23 +2495,23 @@
       <c r="H23" s="8"/>
     </row>
     <row r="24" ht="165" customHeight="1" spans="2:8">
-      <c r="B24" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26">
+      <c r="B24" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23">
         <v>4</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="23">
         <v>5</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="23">
         <v>20</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="25"/>
+      <c r="H24" s="22"/>
     </row>
     <row r="25" ht="165" customHeight="1"/>
     <row r="26" ht="165" customHeight="1"/>

--- a/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
+++ b/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,303 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_392591B29E72432FA41CF03BA0F1B727"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="11849100"/>
+          <a:ext cx="10391775" cy="7886700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_91C2475CCE064031B63A51433BF60115"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="16040100"/>
+          <a:ext cx="10410825" cy="7886700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_34D919B4DB5D4FDAABE71BD01DADB89B"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="26517600"/>
+          <a:ext cx="9953625" cy="7534275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_9B94600C12FF43E593572AD80B6AAB69"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="13944600"/>
+          <a:ext cx="10477500" cy="7915275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_31F23070C9DF4203AB377358DA0E40BE"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="30708600"/>
+          <a:ext cx="8982075" cy="6781800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="ID_E82590AD3933413292F5E4A7EF82149F"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="34899600"/>
+          <a:ext cx="10687050" cy="7896225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="ID_CCB0D5E0DF1040058BA5D45565009653"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="1371600"/>
+          <a:ext cx="10401300" cy="7896225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="ID_E666A622FD004956A78A5E2FD86D85FC"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="3467100"/>
+          <a:ext cx="10048875" cy="7562850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="ID_AC4D20FFE8494E0092981C761AFF2D19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="5562600"/>
+          <a:ext cx="10372725" cy="7896225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="ID_5FC38DA33FF84878884345963C2F805C"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="7658100"/>
+          <a:ext cx="10439400" cy="7905750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>零件名称：</t>
   </si>
@@ -123,6 +418,9 @@
   </si>
   <si>
     <t>钣金快拆垫块</t>
+  </si>
+  <si>
+    <t>髋关节连接02</t>
   </si>
 </sst>
 </file>
@@ -135,7 +433,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -181,6 +479,13 @@
     <font>
       <sz val="10.5"/>
       <color theme="1" tint="0.05"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -724,152 +1029,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -939,6 +1244,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1133,19 +1441,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>74930</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>56515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2873375</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>2729865</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2066925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPr id="17" name="图片 16"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1158,92 +1466,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="1419225"/>
-          <a:ext cx="2759075" cy="2047875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2825750</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>2071370</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="图片 18"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2514600" y="3495675"/>
-          <a:ext cx="2711450" cy="2042795"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2828925</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>2076450</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="图片 19"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2495550" y="5591175"/>
-          <a:ext cx="2733675" cy="2047875"/>
+          <a:off x="2475230" y="9810115"/>
+          <a:ext cx="2654935" cy="2010410"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1260,32 +1484,32 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>78740</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2827020</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>2089150</xdr:rowOff>
+      <xdr:colOff>2764155</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>6985</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="图片 22"/>
+        <xdr:cNvPr id="28" name="图片 27"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2476500" y="7667625"/>
-          <a:ext cx="2750820" cy="2079625"/>
+          <a:off x="2476500" y="18214340"/>
+          <a:ext cx="2687955" cy="2023745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1301,33 +1525,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>62230</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>46990</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2813050</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>2085975</xdr:rowOff>
+      <xdr:colOff>2695575</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2039620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="图片 24"/>
+        <xdr:cNvPr id="29" name="图片 28"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="11877675"/>
-          <a:ext cx="2755900" cy="2057400"/>
+          <a:off x="2462530" y="20278090"/>
+          <a:ext cx="2633345" cy="1992630"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1343,117 +1567,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>27940</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2823210</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2066290</xdr:rowOff>
+      <xdr:colOff>2756535</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2077720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="图片 30"/>
+        <xdr:cNvPr id="30" name="图片 29"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2476500" y="24441150"/>
-          <a:ext cx="2747010" cy="2047240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2754630</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>2058035</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2476500" y="9810750"/>
-          <a:ext cx="2678430" cy="2000885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2808605</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>2077720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2447925" y="18173700"/>
-          <a:ext cx="2760980" cy="2039620"/>
+          <a:off x="2428240" y="22347555"/>
+          <a:ext cx="2728595" cy="2056765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1470,32 +1610,32 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>24765</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>18415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2746375</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2082165</xdr:rowOff>
+      <xdr:colOff>2721610</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2066925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPr id="32" name="图片 31"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
+        <a:blip r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2425065" y="28631515"/>
-          <a:ext cx="2721610" cy="2063750"/>
+          <a:off x="2425065" y="24440515"/>
+          <a:ext cx="2696845" cy="2048510"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1511,33 +1651,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>38735</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>27940</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2787650</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>2083435</xdr:rowOff>
+      <xdr:colOff>2741930</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2075180</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="图片 9"/>
+        <xdr:cNvPr id="34" name="图片 33"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2439035" y="30737175"/>
-          <a:ext cx="2748915" cy="2054860"/>
+          <a:off x="2428240" y="28634055"/>
+          <a:ext cx="2713990" cy="2054225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1553,243 +1693,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>37465</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>37465</xdr:rowOff>
+      <xdr:rowOff>27940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2783205</xdr:colOff>
+      <xdr:colOff>2745740</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>2068830</xdr:rowOff>
+      <xdr:rowOff>2080260</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPr id="36" name="图片 35"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="32841565"/>
-          <a:ext cx="2726055" cy="2031365"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2752090</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2052320</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="26527125"/>
-          <a:ext cx="2713990" cy="2042795"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2773680</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>2068195</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="图片 15"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="20250150"/>
-          <a:ext cx="2735580" cy="2049145"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2799080</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>2067560</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="图片 17"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2447925" y="13954125"/>
-          <a:ext cx="2751455" cy="2058035"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2835910</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2087880</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="图片 20"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="22326600"/>
-          <a:ext cx="2797810" cy="2087880"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2811780</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>2070100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="图片 21"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2476500" y="16059150"/>
-          <a:ext cx="2735580" cy="2051050"/>
+          <a:off x="2437765" y="32832040"/>
+          <a:ext cx="2708275" cy="2052320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2122,7 +2052,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46269</v>
+        <v>46290</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2176,19 +2106,19 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
     </row>
     <row r="8" ht="13.5" spans="1:8">
       <c r="A8" s="1"/>
@@ -2203,7 +2133,10 @@
       <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8"/>
+      <c r="C9" s="8" t="str">
+        <f>_xlfn.DISPIMG("ID_CCB0D5E0DF1040058BA5D45565009653",1)</f>
+        <v>=DISPIMG("ID_CCB0D5E0DF1040058BA5D45565009653",1)</v>
+      </c>
       <c r="D9" s="9">
         <v>2</v>
       </c>
@@ -2223,7 +2156,10 @@
       <c r="B10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_E666A622FD004956A78A5E2FD86D85FC",1)</f>
+        <v>=DISPIMG("ID_E666A622FD004956A78A5E2FD86D85FC",1)</v>
+      </c>
       <c r="D10" s="9">
         <v>2</v>
       </c>
@@ -2242,7 +2178,10 @@
       <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13"/>
+      <c r="C11" s="13" t="str">
+        <f>_xlfn.DISPIMG("ID_AC4D20FFE8494E0092981C761AFF2D19",1)</f>
+        <v>=DISPIMG("ID_AC4D20FFE8494E0092981C761AFF2D19",1)</v>
+      </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
@@ -2262,7 +2201,10 @@
       <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_5FC38DA33FF84878884345963C2F805C",1)</f>
+        <v>=DISPIMG("ID_5FC38DA33FF84878884345963C2F805C",1)</v>
+      </c>
       <c r="D12" s="9">
         <v>2</v>
       </c>
@@ -2302,7 +2244,10 @@
       <c r="B14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="12"/>
+      <c r="C14" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_392591B29E72432FA41CF03BA0F1B727",1)</f>
+        <v>=DISPIMG("ID_392591B29E72432FA41CF03BA0F1B727",1)</v>
+      </c>
       <c r="D14" s="9">
         <v>2</v>
       </c>
@@ -2322,7 +2267,10 @@
       <c r="B15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="12"/>
+      <c r="C15" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_9B94600C12FF43E593572AD80B6AAB69",1)</f>
+        <v>=DISPIMG("ID_9B94600C12FF43E593572AD80B6AAB69",1)</v>
+      </c>
       <c r="D15" s="9">
         <v>4</v>
       </c>
@@ -2343,7 +2291,10 @@
       <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="12"/>
+      <c r="C16" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_91C2475CCE064031B63A51433BF60115",1)</f>
+        <v>=DISPIMG("ID_91C2475CCE064031B63A51433BF60115",1)</v>
+      </c>
       <c r="D16" s="9">
         <v>4</v>
       </c>
@@ -2405,13 +2356,13 @@
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" s="9">
         <v>5</v>
       </c>
       <c r="F19" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>13</v>
@@ -2441,7 +2392,10 @@
       <c r="B21" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="8"/>
+      <c r="C21" s="8" t="str">
+        <f>_xlfn.DISPIMG("ID_34D919B4DB5D4FDAABE71BD01DADB89B",1)</f>
+        <v>=DISPIMG("ID_34D919B4DB5D4FDAABE71BD01DADB89B",1)</v>
+      </c>
       <c r="D21" s="9">
         <v>2</v>
       </c>
@@ -2462,13 +2416,13 @@
       </c>
       <c r="C22" s="22"/>
       <c r="D22" s="23">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E22" s="23">
         <v>5</v>
       </c>
       <c r="F22" s="23">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>13</v>
@@ -2479,7 +2433,10 @@
       <c r="B23" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="8"/>
+      <c r="C23" s="8" t="str">
+        <f>_xlfn.DISPIMG("ID_31F23070C9DF4203AB377358DA0E40BE",1)</f>
+        <v>=DISPIMG("ID_31F23070C9DF4203AB377358DA0E40BE",1)</v>
+      </c>
       <c r="D23" s="9">
         <v>8</v>
       </c>
@@ -2513,7 +2470,28 @@
       </c>
       <c r="H24" s="22"/>
     </row>
-    <row r="25" ht="165" customHeight="1"/>
+    <row r="25" ht="165" customHeight="1" spans="2:8">
+      <c r="B25" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="22" t="str">
+        <f>_xlfn.DISPIMG("ID_E82590AD3933413292F5E4A7EF82149F",1)</f>
+        <v>=DISPIMG("ID_E82590AD3933413292F5E4A7EF82149F",1)</v>
+      </c>
+      <c r="D25" s="23">
+        <v>4</v>
+      </c>
+      <c r="E25" s="23">
+        <v>5</v>
+      </c>
+      <c r="F25" s="23">
+        <v>20</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="22"/>
+    </row>
     <row r="26" ht="165" customHeight="1"/>
     <row r="27" ht="165" customHeight="1"/>
   </sheetData>

--- a/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
+++ b/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_392591B29E72432FA41CF03BA0F1B727"/>
+        <xdr:cNvPr id="2" name="ID_98FEBC93A2394ACC8182D665446EBDA6"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -44,8 +44,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="11849100"/>
-          <a:ext cx="10391775" cy="7886700"/>
+          <a:off x="2400300" y="1371600"/>
+          <a:ext cx="9972675" cy="7543800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -60,7 +60,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_91C2475CCE064031B63A51433BF60115"/>
+        <xdr:cNvPr id="12" name="ID_C78908968D4048C89B2FF96CD5F2D64A"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -73,36 +73,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="16040100"/>
-          <a:ext cx="10410825" cy="7886700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_34D919B4DB5D4FDAABE71BD01DADB89B"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2400300" y="26517600"/>
+          <a:off x="2400300" y="3467100"/>
           <a:ext cx="9953625" cy="7534275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -118,21 +89,21 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_9B94600C12FF43E593572AD80B6AAB69"/>
+        <xdr:cNvPr id="13" name="ID_2F5569B350B843569A46F53A31EFBBC1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="13944600"/>
-          <a:ext cx="10477500" cy="7915275"/>
+          <a:off x="2400300" y="5562600"/>
+          <a:ext cx="9991725" cy="7534275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -147,21 +118,21 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="ID_31F23070C9DF4203AB377358DA0E40BE"/>
+        <xdr:cNvPr id="15" name="ID_EF84482744414917A51F85DCBB6F2E6C"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="30708600"/>
-          <a:ext cx="8982075" cy="6781800"/>
+          <a:off x="2400300" y="7658100"/>
+          <a:ext cx="10420350" cy="7886700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -176,21 +147,21 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="ID_E82590AD3933413292F5E4A7EF82149F"/>
+        <xdr:cNvPr id="16" name="ID_92B867FD823F4439862BCBAEC59DB6CC"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="34899600"/>
-          <a:ext cx="10687050" cy="7896225"/>
+          <a:off x="2400300" y="9753600"/>
+          <a:ext cx="10467975" cy="7886700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -205,21 +176,21 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="ID_CCB0D5E0DF1040058BA5D45565009653"/>
+        <xdr:cNvPr id="17" name="ID_65BF606A66D9456AAED2E244E68E390A"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="1371600"/>
-          <a:ext cx="10401300" cy="7896225"/>
+          <a:off x="2400300" y="11849100"/>
+          <a:ext cx="10096500" cy="7543800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -234,21 +205,21 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="ID_E666A622FD004956A78A5E2FD86D85FC"/>
+        <xdr:cNvPr id="18" name="ID_F142DB63E88C453FA5000CBD5A718A02"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
+        <a:blip r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="3467100"/>
-          <a:ext cx="10048875" cy="7562850"/>
+          <a:off x="2400300" y="13944600"/>
+          <a:ext cx="10029825" cy="7543800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -263,21 +234,21 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="ID_AC4D20FFE8494E0092981C761AFF2D19"/>
+        <xdr:cNvPr id="19" name="ID_EAE5F71FF11C45829A67A13B34E9ED07"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
+        <a:blip r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="5562600"/>
-          <a:ext cx="10372725" cy="7896225"/>
+          <a:off x="2400300" y="18135600"/>
+          <a:ext cx="10639425" cy="7886700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -292,7 +263,36 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="ID_5FC38DA33FF84878884345963C2F805C"/>
+        <xdr:cNvPr id="20" name="ID_BF6E2A1DC4414280BE5287309DC7F8E9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="22326600"/>
+          <a:ext cx="9972675" cy="7515225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="ID_68A0CC8FFB51431EBB190C76FFE0D3F4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -305,8 +305,153 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2400300" y="7658100"/>
-          <a:ext cx="10439400" cy="7905750"/>
+          <a:off x="2400300" y="24422100"/>
+          <a:ext cx="9991725" cy="7543800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="ID_8CC4F7A1D1874401A3C3D488F4642E9A"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="26517600"/>
+          <a:ext cx="9982200" cy="7534275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="ID_53068F6D5F77428BBB7B42C8F6BFDC29"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="30708600"/>
+          <a:ext cx="9934575" cy="7543800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="ID_5D10114969984C1B9BE4A8B09522B1BE"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="32804100"/>
+          <a:ext cx="10629900" cy="7886700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_199F30A043134A75A748114111F389A6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="34899600"/>
+          <a:ext cx="10648950" cy="7839075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_DD105294A4E8472BACC1CE0CCC2EFD1C"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="28613100"/>
+          <a:ext cx="10706100" cy="7877175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -399,9 +544,6 @@
     <t>45钢</t>
   </si>
   <si>
-    <t>肘关节连接A</t>
-  </si>
-  <si>
     <t>肘关节连接B</t>
   </si>
   <si>
@@ -414,13 +556,16 @@
     <t>大腿关节限位块</t>
   </si>
   <si>
-    <t>髋关节限位块</t>
+    <t>髋关节电机输出支撑</t>
   </si>
   <si>
     <t>钣金快拆垫块</t>
   </si>
   <si>
     <t>髋关节连接02</t>
+  </si>
+  <si>
+    <t>小腿</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1319,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1247,6 +1392,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1441,90 +1589,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>74930</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>56515</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2729865</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>2066925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="图片 16"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2475230" y="9810115"/>
-          <a:ext cx="2654935" cy="2010410"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>78740</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2764155</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>6985</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="图片 27"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2476500" y="18214340"/>
-          <a:ext cx="2687955" cy="2023745"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>62230</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>46990</xdr:rowOff>
@@ -1543,7 +1607,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1567,159 +1631,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>27940</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>20955</xdr:rowOff>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2756535</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2077720</xdr:rowOff>
+      <xdr:colOff>2838450</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>2088515</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="图片 29"/>
+        <xdr:cNvPr id="9" name="图片 8"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2428240" y="22347555"/>
-          <a:ext cx="2728595" cy="2056765"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>24765</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>18415</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2721610</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2066925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="图片 31"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2425065" y="24440515"/>
-          <a:ext cx="2696845" cy="2048510"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>27940</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>20955</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2741930</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2075180</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="图片 33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2428240" y="28634055"/>
-          <a:ext cx="2713990" cy="2054225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>37465</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2745740</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>2080260</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="图片 35"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2437765" y="32832040"/>
-          <a:ext cx="2708275" cy="2052320"/>
+          <a:off x="2505075" y="16059150"/>
+          <a:ext cx="2733675" cy="2069465"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1995,7 +1933,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -2052,7 +1990,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46290</v>
+        <v>46314</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2106,19 +2044,19 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
     </row>
     <row r="8" ht="13.5" spans="1:8">
       <c r="A8" s="1"/>
@@ -2134,8 +2072,8 @@
         <v>12</v>
       </c>
       <c r="C9" s="8" t="str">
-        <f>_xlfn.DISPIMG("ID_CCB0D5E0DF1040058BA5D45565009653",1)</f>
-        <v>=DISPIMG("ID_CCB0D5E0DF1040058BA5D45565009653",1)</v>
+        <f>_xlfn.DISPIMG("ID_98FEBC93A2394ACC8182D665446EBDA6",1)</f>
+        <v>=DISPIMG("ID_98FEBC93A2394ACC8182D665446EBDA6",1)</v>
       </c>
       <c r="D9" s="9">
         <v>2</v>
@@ -2157,8 +2095,8 @@
         <v>14</v>
       </c>
       <c r="C10" s="12" t="str">
-        <f>_xlfn.DISPIMG("ID_E666A622FD004956A78A5E2FD86D85FC",1)</f>
-        <v>=DISPIMG("ID_E666A622FD004956A78A5E2FD86D85FC",1)</v>
+        <f>_xlfn.DISPIMG("ID_C78908968D4048C89B2FF96CD5F2D64A",1)</f>
+        <v>=DISPIMG("ID_C78908968D4048C89B2FF96CD5F2D64A",1)</v>
       </c>
       <c r="D10" s="9">
         <v>2</v>
@@ -2179,8 +2117,8 @@
         <v>15</v>
       </c>
       <c r="C11" s="13" t="str">
-        <f>_xlfn.DISPIMG("ID_AC4D20FFE8494E0092981C761AFF2D19",1)</f>
-        <v>=DISPIMG("ID_AC4D20FFE8494E0092981C761AFF2D19",1)</v>
+        <f>_xlfn.DISPIMG("ID_2F5569B350B843569A46F53A31EFBBC1",1)</f>
+        <v>=DISPIMG("ID_2F5569B350B843569A46F53A31EFBBC1",1)</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
@@ -2202,8 +2140,8 @@
         <v>16</v>
       </c>
       <c r="C12" s="12" t="str">
-        <f>_xlfn.DISPIMG("ID_5FC38DA33FF84878884345963C2F805C",1)</f>
-        <v>=DISPIMG("ID_5FC38DA33FF84878884345963C2F805C",1)</v>
+        <f>_xlfn.DISPIMG("ID_EF84482744414917A51F85DCBB6F2E6C",1)</f>
+        <v>=DISPIMG("ID_EF84482744414917A51F85DCBB6F2E6C",1)</v>
       </c>
       <c r="D12" s="9">
         <v>2</v>
@@ -2224,7 +2162,10 @@
       <c r="B13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="12"/>
+      <c r="C13" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_92B867FD823F4439862BCBAEC59DB6CC",1)</f>
+        <v>=DISPIMG("ID_92B867FD823F4439862BCBAEC59DB6CC",1)</v>
+      </c>
       <c r="D13" s="9">
         <v>8</v>
       </c>
@@ -2245,8 +2186,8 @@
         <v>18</v>
       </c>
       <c r="C14" s="12" t="str">
-        <f>_xlfn.DISPIMG("ID_392591B29E72432FA41CF03BA0F1B727",1)</f>
-        <v>=DISPIMG("ID_392591B29E72432FA41CF03BA0F1B727",1)</v>
+        <f>_xlfn.DISPIMG("ID_65BF606A66D9456AAED2E244E68E390A",1)</f>
+        <v>=DISPIMG("ID_65BF606A66D9456AAED2E244E68E390A",1)</v>
       </c>
       <c r="D14" s="9">
         <v>2</v>
@@ -2268,8 +2209,8 @@
         <v>19</v>
       </c>
       <c r="C15" s="12" t="str">
-        <f>_xlfn.DISPIMG("ID_9B94600C12FF43E593572AD80B6AAB69",1)</f>
-        <v>=DISPIMG("ID_9B94600C12FF43E593572AD80B6AAB69",1)</v>
+        <f>_xlfn.DISPIMG("ID_F142DB63E88C453FA5000CBD5A718A02",1)</f>
+        <v>=DISPIMG("ID_F142DB63E88C453FA5000CBD5A718A02",1)</v>
       </c>
       <c r="D15" s="9">
         <v>4</v>
@@ -2291,10 +2232,7 @@
       <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="12" t="str">
-        <f>_xlfn.DISPIMG("ID_91C2475CCE064031B63A51433BF60115",1)</f>
-        <v>=DISPIMG("ID_91C2475CCE064031B63A51433BF60115",1)</v>
-      </c>
+      <c r="C16" s="12"/>
       <c r="D16" s="9">
         <v>4</v>
       </c>
@@ -2315,7 +2253,10 @@
       <c r="B17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="12"/>
+      <c r="C17" s="12" t="str">
+        <f>_xlfn.DISPIMG("ID_EAE5F71FF11C45829A67A13B34E9ED07",1)</f>
+        <v>=DISPIMG("ID_EAE5F71FF11C45829A67A13B34E9ED07",1)</v>
+      </c>
       <c r="D17" s="9">
         <v>2</v>
       </c>
@@ -2351,121 +2292,133 @@
       <c r="H18" s="13"/>
     </row>
     <row r="19" ht="165" customHeight="1" spans="2:8">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="9">
+      <c r="C19" s="16" t="str">
+        <f>_xlfn.DISPIMG("ID_BF6E2A1DC4414280BE5287309DC7F8E9",1)</f>
+        <v>=DISPIMG("ID_BF6E2A1DC4414280BE5287309DC7F8E9",1)</v>
+      </c>
+      <c r="D19" s="17">
         <v>4</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="17">
         <v>5</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="17">
         <v>20</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="13"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" ht="165" customHeight="1" spans="2:8">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17">
-        <v>4</v>
-      </c>
-      <c r="E20" s="17">
+      <c r="C20" s="8" t="str">
+        <f>_xlfn.DISPIMG("ID_68A0CC8FFB51431EBB190C76FFE0D3F4",1)</f>
+        <v>=DISPIMG("ID_68A0CC8FFB51431EBB190C76FFE0D3F4",1)</v>
+      </c>
+      <c r="D20" s="9">
+        <v>2</v>
+      </c>
+      <c r="E20" s="9">
         <v>5</v>
       </c>
-      <c r="F20" s="17">
-        <v>20</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="19"/>
+      <c r="F20" s="9">
+        <v>10</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" ht="165" customHeight="1" spans="2:8">
-      <c r="B21" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="8" t="str">
-        <f>_xlfn.DISPIMG("ID_34D919B4DB5D4FDAABE71BD01DADB89B",1)</f>
-        <v>=DISPIMG("ID_34D919B4DB5D4FDAABE71BD01DADB89B",1)</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="B21" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="22" t="str">
+        <f>_xlfn.DISPIMG("ID_8CC4F7A1D1874401A3C3D488F4642E9A",1)</f>
+        <v>=DISPIMG("ID_8CC4F7A1D1874401A3C3D488F4642E9A",1)</v>
+      </c>
+      <c r="D21" s="23">
+        <v>4</v>
+      </c>
+      <c r="E21" s="23">
         <v>5</v>
       </c>
-      <c r="F21" s="9">
-        <v>10</v>
+      <c r="F21" s="23">
+        <v>20</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="H21" s="22"/>
     </row>
     <row r="22" ht="165" customHeight="1" spans="2:8">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="23">
+      <c r="C22" s="8" t="str">
+        <f>_xlfn.DISPIMG("ID_DD105294A4E8472BACC1CE0CCC2EFD1C",1)</f>
+        <v>=DISPIMG("ID_DD105294A4E8472BACC1CE0CCC2EFD1C",1)</v>
+      </c>
+      <c r="D22" s="9">
         <v>4</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="9">
         <v>5</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="9">
         <v>20</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="22"/>
+      <c r="H22" s="8"/>
     </row>
     <row r="23" ht="165" customHeight="1" spans="2:8">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="8" t="str">
-        <f>_xlfn.DISPIMG("ID_31F23070C9DF4203AB377358DA0E40BE",1)</f>
-        <v>=DISPIMG("ID_31F23070C9DF4203AB377358DA0E40BE",1)</v>
-      </c>
-      <c r="D23" s="9">
-        <v>8</v>
-      </c>
-      <c r="E23" s="9">
+      <c r="C23" s="22" t="str">
+        <f>_xlfn.DISPIMG("ID_53068F6D5F77428BBB7B42C8F6BFDC29",1)</f>
+        <v>=DISPIMG("ID_53068F6D5F77428BBB7B42C8F6BFDC29",1)</v>
+      </c>
+      <c r="D23" s="23">
+        <v>4</v>
+      </c>
+      <c r="E23" s="23">
         <v>5</v>
       </c>
-      <c r="F23" s="9">
-        <v>40</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="23">
+        <v>20</v>
+      </c>
+      <c r="G23" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" ht="165" customHeight="1" spans="2:8">
       <c r="B24" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="22" t="str">
+        <f>_xlfn.DISPIMG("ID_5D10114969984C1B9BE4A8B09522B1BE",1)</f>
+        <v>=DISPIMG("ID_5D10114969984C1B9BE4A8B09522B1BE",1)</v>
+      </c>
       <c r="D24" s="23">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" s="23">
         <v>5</v>
       </c>
       <c r="F24" s="23">
-        <v>20</v>
-      </c>
-      <c r="G24" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="25" t="s">
         <v>13</v>
       </c>
       <c r="H24" s="22"/>
@@ -2475,8 +2428,8 @@
         <v>32</v>
       </c>
       <c r="C25" s="22" t="str">
-        <f>_xlfn.DISPIMG("ID_E82590AD3933413292F5E4A7EF82149F",1)</f>
-        <v>=DISPIMG("ID_E82590AD3933413292F5E4A7EF82149F",1)</v>
+        <f>_xlfn.DISPIMG("ID_199F30A043134A75A748114111F389A6",1)</f>
+        <v>=DISPIMG("ID_199F30A043134A75A748114111F389A6",1)</v>
       </c>
       <c r="D25" s="23">
         <v>4</v>
@@ -2487,13 +2440,12 @@
       <c r="F25" s="23">
         <v>20</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="26" t="s">
         <v>13</v>
       </c>
       <c r="H25" s="22"/>
     </row>
     <row r="26" ht="165" customHeight="1"/>
-    <row r="27" ht="165" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
+++ b/四足-夏元瑞-5套/四足-夏元瑞-5套.xlsx
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
